--- a/Info/Progress Tracker.xlsx
+++ b/Info/Progress Tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/will/Desktop/Project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/will/Desktop/Project/Info/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8A9465A-D701-FB45-812D-1F7213D1FA6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5978350-0AA0-F447-90BB-32274EAFDDFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1421,6 +1421,22 @@
     <xf numFmtId="167" fontId="15" fillId="12" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="22" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1439,22 +1455,6 @@
     <xf numFmtId="0" fontId="23" fillId="19" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
-    <xf numFmtId="166" fontId="22" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="13">
     <cellStyle name="Comma" xfId="4" builtinId="3" customBuiltin="1"/>
@@ -1605,23 +1605,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="4" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-4.9989318521683403E-2"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
@@ -1644,6 +1627,23 @@
         </right>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-4.9989318521683403E-2"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -2274,57 +2274,57 @@
       <c r="D1" s="8"/>
       <c r="E1" s="9"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="123" t="s">
+      <c r="H1" s="129" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="124"/>
-      <c r="J1" s="124"/>
-      <c r="K1" s="124"/>
-      <c r="L1" s="124"/>
-      <c r="M1" s="124"/>
-      <c r="N1" s="124"/>
+      <c r="I1" s="130"/>
+      <c r="J1" s="130"/>
+      <c r="K1" s="130"/>
+      <c r="L1" s="130"/>
+      <c r="M1" s="130"/>
+      <c r="N1" s="130"/>
       <c r="O1" s="12"/>
-      <c r="P1" s="121">
+      <c r="P1" s="127">
         <f>DATE(2026,5,6)</f>
         <v>46148</v>
       </c>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
+      <c r="Q1" s="128"/>
+      <c r="R1" s="128"/>
+      <c r="S1" s="128"/>
+      <c r="T1" s="128"/>
+      <c r="U1" s="128"/>
+      <c r="V1" s="128"/>
+      <c r="W1" s="128"/>
+      <c r="X1" s="128"/>
+      <c r="Y1" s="128"/>
     </row>
     <row r="2" spans="1:142" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="50"/>
       <c r="C2" s="10"/>
       <c r="D2" s="11"/>
       <c r="E2" s="10"/>
-      <c r="H2" s="123" t="s">
+      <c r="H2" s="129" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="124"/>
-      <c r="J2" s="124"/>
-      <c r="K2" s="124"/>
-      <c r="L2" s="124"/>
-      <c r="M2" s="124"/>
-      <c r="N2" s="124"/>
+      <c r="I2" s="130"/>
+      <c r="J2" s="130"/>
+      <c r="K2" s="130"/>
+      <c r="L2" s="130"/>
+      <c r="M2" s="130"/>
+      <c r="N2" s="130"/>
       <c r="O2" s="12"/>
-      <c r="P2" s="119">
+      <c r="P2" s="125">
         <v>1</v>
       </c>
-      <c r="Q2" s="120"/>
-      <c r="R2" s="120"/>
-      <c r="S2" s="120"/>
-      <c r="T2" s="120"/>
-      <c r="U2" s="120"/>
-      <c r="V2" s="120"/>
-      <c r="W2" s="120"/>
-      <c r="X2" s="120"/>
-      <c r="Y2" s="120"/>
+      <c r="Q2" s="126"/>
+      <c r="R2" s="126"/>
+      <c r="S2" s="126"/>
+      <c r="T2" s="126"/>
+      <c r="U2" s="126"/>
+      <c r="V2" s="126"/>
+      <c r="W2" s="126"/>
+      <c r="X2" s="126"/>
+      <c r="Y2" s="126"/>
     </row>
     <row r="3" spans="1:142" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="4"/>
@@ -2336,162 +2336,162 @@
       <c r="A4" s="5"/>
       <c r="B4" s="17"/>
       <c r="D4" s="18"/>
-      <c r="H4" s="127" t="s">
+      <c r="H4" s="124" t="s">
         <v>54</v>
       </c>
-      <c r="I4" s="127"/>
-      <c r="J4" s="127"/>
-      <c r="K4" s="127"/>
-      <c r="L4" s="127"/>
-      <c r="M4" s="127"/>
-      <c r="N4" s="127"/>
-      <c r="O4" s="127"/>
-      <c r="P4" s="127"/>
-      <c r="Q4" s="127"/>
-      <c r="R4" s="127"/>
-      <c r="S4" s="127"/>
-      <c r="T4" s="127"/>
-      <c r="U4" s="127"/>
-      <c r="V4" s="127"/>
-      <c r="W4" s="127"/>
-      <c r="X4" s="127"/>
-      <c r="Y4" s="127"/>
-      <c r="Z4" s="127"/>
-      <c r="AA4" s="127"/>
-      <c r="AB4" s="127"/>
-      <c r="AC4" s="127"/>
-      <c r="AD4" s="127"/>
-      <c r="AE4" s="127"/>
-      <c r="AF4" s="127"/>
-      <c r="AG4" s="127"/>
-      <c r="AH4" s="127"/>
-      <c r="AI4" s="127"/>
-      <c r="AJ4" s="127" t="s">
+      <c r="I4" s="124"/>
+      <c r="J4" s="124"/>
+      <c r="K4" s="124"/>
+      <c r="L4" s="124"/>
+      <c r="M4" s="124"/>
+      <c r="N4" s="124"/>
+      <c r="O4" s="124"/>
+      <c r="P4" s="124"/>
+      <c r="Q4" s="124"/>
+      <c r="R4" s="124"/>
+      <c r="S4" s="124"/>
+      <c r="T4" s="124"/>
+      <c r="U4" s="124"/>
+      <c r="V4" s="124"/>
+      <c r="W4" s="124"/>
+      <c r="X4" s="124"/>
+      <c r="Y4" s="124"/>
+      <c r="Z4" s="124"/>
+      <c r="AA4" s="124"/>
+      <c r="AB4" s="124"/>
+      <c r="AC4" s="124"/>
+      <c r="AD4" s="124"/>
+      <c r="AE4" s="124"/>
+      <c r="AF4" s="124"/>
+      <c r="AG4" s="124"/>
+      <c r="AH4" s="124"/>
+      <c r="AI4" s="124"/>
+      <c r="AJ4" s="124" t="s">
         <v>55</v>
       </c>
-      <c r="AK4" s="127"/>
-      <c r="AL4" s="127"/>
-      <c r="AM4" s="127"/>
-      <c r="AN4" s="127"/>
-      <c r="AO4" s="127"/>
-      <c r="AP4" s="127"/>
-      <c r="AQ4" s="127"/>
-      <c r="AR4" s="127"/>
-      <c r="AS4" s="127"/>
-      <c r="AT4" s="127"/>
-      <c r="AU4" s="127"/>
-      <c r="AV4" s="127"/>
-      <c r="AW4" s="127"/>
-      <c r="AX4" s="127"/>
-      <c r="AY4" s="127"/>
-      <c r="AZ4" s="127"/>
-      <c r="BA4" s="127"/>
-      <c r="BB4" s="127"/>
-      <c r="BC4" s="127"/>
-      <c r="BD4" s="127"/>
-      <c r="BE4" s="127"/>
-      <c r="BF4" s="127"/>
-      <c r="BG4" s="127"/>
-      <c r="BH4" s="127"/>
-      <c r="BI4" s="127"/>
-      <c r="BJ4" s="127"/>
-      <c r="BK4" s="127"/>
-      <c r="BL4" s="127"/>
-      <c r="BM4" s="127"/>
-      <c r="BN4" s="127" t="s">
+      <c r="AK4" s="124"/>
+      <c r="AL4" s="124"/>
+      <c r="AM4" s="124"/>
+      <c r="AN4" s="124"/>
+      <c r="AO4" s="124"/>
+      <c r="AP4" s="124"/>
+      <c r="AQ4" s="124"/>
+      <c r="AR4" s="124"/>
+      <c r="AS4" s="124"/>
+      <c r="AT4" s="124"/>
+      <c r="AU4" s="124"/>
+      <c r="AV4" s="124"/>
+      <c r="AW4" s="124"/>
+      <c r="AX4" s="124"/>
+      <c r="AY4" s="124"/>
+      <c r="AZ4" s="124"/>
+      <c r="BA4" s="124"/>
+      <c r="BB4" s="124"/>
+      <c r="BC4" s="124"/>
+      <c r="BD4" s="124"/>
+      <c r="BE4" s="124"/>
+      <c r="BF4" s="124"/>
+      <c r="BG4" s="124"/>
+      <c r="BH4" s="124"/>
+      <c r="BI4" s="124"/>
+      <c r="BJ4" s="124"/>
+      <c r="BK4" s="124"/>
+      <c r="BL4" s="124"/>
+      <c r="BM4" s="124"/>
+      <c r="BN4" s="124" t="s">
         <v>56</v>
       </c>
-      <c r="BO4" s="127"/>
-      <c r="BP4" s="127"/>
-      <c r="BQ4" s="127"/>
-      <c r="BR4" s="127"/>
-      <c r="BS4" s="127"/>
-      <c r="BT4" s="127"/>
-      <c r="BU4" s="127"/>
-      <c r="BV4" s="127"/>
-      <c r="BW4" s="127"/>
-      <c r="BX4" s="127"/>
-      <c r="BY4" s="127"/>
-      <c r="BZ4" s="127"/>
-      <c r="CA4" s="127"/>
-      <c r="CB4" s="127"/>
-      <c r="CC4" s="127"/>
-      <c r="CD4" s="127"/>
-      <c r="CE4" s="127"/>
-      <c r="CF4" s="127"/>
-      <c r="CG4" s="127"/>
-      <c r="CH4" s="127"/>
-      <c r="CI4" s="127"/>
-      <c r="CJ4" s="127"/>
-      <c r="CK4" s="127"/>
-      <c r="CL4" s="127"/>
-      <c r="CM4" s="127"/>
-      <c r="CN4" s="127"/>
-      <c r="CO4" s="127"/>
-      <c r="CP4" s="127"/>
-      <c r="CQ4" s="127"/>
-      <c r="CR4" s="127"/>
-      <c r="CS4" s="127" t="s">
+      <c r="BO4" s="124"/>
+      <c r="BP4" s="124"/>
+      <c r="BQ4" s="124"/>
+      <c r="BR4" s="124"/>
+      <c r="BS4" s="124"/>
+      <c r="BT4" s="124"/>
+      <c r="BU4" s="124"/>
+      <c r="BV4" s="124"/>
+      <c r="BW4" s="124"/>
+      <c r="BX4" s="124"/>
+      <c r="BY4" s="124"/>
+      <c r="BZ4" s="124"/>
+      <c r="CA4" s="124"/>
+      <c r="CB4" s="124"/>
+      <c r="CC4" s="124"/>
+      <c r="CD4" s="124"/>
+      <c r="CE4" s="124"/>
+      <c r="CF4" s="124"/>
+      <c r="CG4" s="124"/>
+      <c r="CH4" s="124"/>
+      <c r="CI4" s="124"/>
+      <c r="CJ4" s="124"/>
+      <c r="CK4" s="124"/>
+      <c r="CL4" s="124"/>
+      <c r="CM4" s="124"/>
+      <c r="CN4" s="124"/>
+      <c r="CO4" s="124"/>
+      <c r="CP4" s="124"/>
+      <c r="CQ4" s="124"/>
+      <c r="CR4" s="124"/>
+      <c r="CS4" s="124" t="s">
         <v>57</v>
       </c>
-      <c r="CT4" s="127"/>
-      <c r="CU4" s="127"/>
-      <c r="CV4" s="127"/>
-      <c r="CW4" s="127"/>
-      <c r="CX4" s="127"/>
-      <c r="CY4" s="127"/>
-      <c r="CZ4" s="127"/>
-      <c r="DA4" s="127"/>
-      <c r="DB4" s="127"/>
-      <c r="DC4" s="127"/>
-      <c r="DD4" s="127"/>
-      <c r="DE4" s="127"/>
-      <c r="DF4" s="127"/>
-      <c r="DG4" s="127"/>
-      <c r="DH4" s="127"/>
-      <c r="DI4" s="127"/>
-      <c r="DJ4" s="127"/>
-      <c r="DK4" s="127"/>
-      <c r="DL4" s="127"/>
-      <c r="DM4" s="127"/>
-      <c r="DN4" s="127"/>
-      <c r="DO4" s="127"/>
-      <c r="DP4" s="127"/>
-      <c r="DQ4" s="127"/>
-      <c r="DR4" s="127"/>
-      <c r="DS4" s="127"/>
-      <c r="DT4" s="127"/>
-      <c r="DU4" s="127"/>
-      <c r="DV4" s="127"/>
-      <c r="DW4" s="127"/>
-      <c r="DX4" s="127" t="s">
+      <c r="CT4" s="124"/>
+      <c r="CU4" s="124"/>
+      <c r="CV4" s="124"/>
+      <c r="CW4" s="124"/>
+      <c r="CX4" s="124"/>
+      <c r="CY4" s="124"/>
+      <c r="CZ4" s="124"/>
+      <c r="DA4" s="124"/>
+      <c r="DB4" s="124"/>
+      <c r="DC4" s="124"/>
+      <c r="DD4" s="124"/>
+      <c r="DE4" s="124"/>
+      <c r="DF4" s="124"/>
+      <c r="DG4" s="124"/>
+      <c r="DH4" s="124"/>
+      <c r="DI4" s="124"/>
+      <c r="DJ4" s="124"/>
+      <c r="DK4" s="124"/>
+      <c r="DL4" s="124"/>
+      <c r="DM4" s="124"/>
+      <c r="DN4" s="124"/>
+      <c r="DO4" s="124"/>
+      <c r="DP4" s="124"/>
+      <c r="DQ4" s="124"/>
+      <c r="DR4" s="124"/>
+      <c r="DS4" s="124"/>
+      <c r="DT4" s="124"/>
+      <c r="DU4" s="124"/>
+      <c r="DV4" s="124"/>
+      <c r="DW4" s="124"/>
+      <c r="DX4" s="124" t="s">
         <v>58</v>
       </c>
-      <c r="DY4" s="127"/>
-      <c r="DZ4" s="127"/>
-      <c r="EA4" s="127"/>
-      <c r="EB4" s="127"/>
-      <c r="EC4" s="127"/>
-      <c r="ED4" s="127"/>
-      <c r="EE4" s="127"/>
-      <c r="EF4" s="127"/>
-      <c r="EG4" s="127"/>
-      <c r="EH4" s="127"/>
-      <c r="EI4" s="127"/>
-      <c r="EJ4" s="127"/>
+      <c r="DY4" s="124"/>
+      <c r="DZ4" s="124"/>
+      <c r="EA4" s="124"/>
+      <c r="EB4" s="124"/>
+      <c r="EC4" s="124"/>
+      <c r="ED4" s="124"/>
+      <c r="EE4" s="124"/>
+      <c r="EF4" s="124"/>
+      <c r="EG4" s="124"/>
+      <c r="EH4" s="124"/>
+      <c r="EI4" s="124"/>
+      <c r="EJ4" s="124"/>
     </row>
     <row r="5" spans="1:142" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="128"/>
-      <c r="B5" s="129" t="s">
+      <c r="A5" s="119"/>
+      <c r="B5" s="120" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="131" t="s">
+      <c r="C5" s="122" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="131" t="s">
+      <c r="D5" s="122" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="131" t="s">
+      <c r="E5" s="122" t="s">
         <v>2</v>
       </c>
       <c r="H5" s="116">
@@ -3028,11 +3028,11 @@
       </c>
     </row>
     <row r="6" spans="1:142" s="14" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="128"/>
-      <c r="B6" s="130"/>
-      <c r="C6" s="132"/>
-      <c r="D6" s="132"/>
-      <c r="E6" s="132"/>
+      <c r="A6" s="119"/>
+      <c r="B6" s="121"/>
+      <c r="C6" s="123"/>
+      <c r="D6" s="123"/>
+      <c r="E6" s="123"/>
       <c r="H6" s="19" t="str">
         <f t="shared" ref="H6:AM6" si="60">LEFT(TEXT(H5,"ddd"),1)</f>
         <v>M</v>
@@ -3865,7 +3865,7 @@
         <v>9</v>
       </c>
       <c r="C9" s="31">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="D9" s="51">
         <f>Project_Start</f>
@@ -3977,22 +3977,22 @@
       <c r="CY9" s="32"/>
       <c r="CZ9" s="32"/>
       <c r="DA9" s="32"/>
-      <c r="DB9" s="125" t="s">
+      <c r="DB9" s="131" t="s">
         <v>53</v>
       </c>
-      <c r="DC9" s="125"/>
-      <c r="DD9" s="125"/>
-      <c r="DE9" s="125"/>
-      <c r="DF9" s="125"/>
-      <c r="DG9" s="125"/>
-      <c r="DH9" s="125"/>
-      <c r="DI9" s="125"/>
-      <c r="DJ9" s="125"/>
-      <c r="DK9" s="125"/>
-      <c r="DL9" s="125"/>
-      <c r="DM9" s="125"/>
-      <c r="DN9" s="125"/>
-      <c r="DO9" s="126"/>
+      <c r="DC9" s="131"/>
+      <c r="DD9" s="131"/>
+      <c r="DE9" s="131"/>
+      <c r="DF9" s="131"/>
+      <c r="DG9" s="131"/>
+      <c r="DH9" s="131"/>
+      <c r="DI9" s="131"/>
+      <c r="DJ9" s="131"/>
+      <c r="DK9" s="131"/>
+      <c r="DL9" s="131"/>
+      <c r="DM9" s="131"/>
+      <c r="DN9" s="131"/>
+      <c r="DO9" s="132"/>
       <c r="DP9" s="114"/>
       <c r="DQ9" s="32"/>
       <c r="DR9" s="32"/>
@@ -4129,20 +4129,20 @@
       <c r="CY10" s="32"/>
       <c r="CZ10" s="32"/>
       <c r="DA10" s="32"/>
-      <c r="DB10" s="125"/>
-      <c r="DC10" s="125"/>
-      <c r="DD10" s="125"/>
-      <c r="DE10" s="125"/>
-      <c r="DF10" s="125"/>
-      <c r="DG10" s="125"/>
-      <c r="DH10" s="125"/>
-      <c r="DI10" s="125"/>
-      <c r="DJ10" s="125"/>
-      <c r="DK10" s="125"/>
-      <c r="DL10" s="125"/>
-      <c r="DM10" s="125"/>
-      <c r="DN10" s="125"/>
-      <c r="DO10" s="126"/>
+      <c r="DB10" s="131"/>
+      <c r="DC10" s="131"/>
+      <c r="DD10" s="131"/>
+      <c r="DE10" s="131"/>
+      <c r="DF10" s="131"/>
+      <c r="DG10" s="131"/>
+      <c r="DH10" s="131"/>
+      <c r="DI10" s="131"/>
+      <c r="DJ10" s="131"/>
+      <c r="DK10" s="131"/>
+      <c r="DL10" s="131"/>
+      <c r="DM10" s="131"/>
+      <c r="DN10" s="131"/>
+      <c r="DO10" s="132"/>
       <c r="DP10" s="114"/>
       <c r="DQ10" s="32"/>
       <c r="DR10" s="32"/>
@@ -4179,7 +4179,7 @@
         <v>12</v>
       </c>
       <c r="C11" s="34">
-        <v>0.12</v>
+        <v>1</v>
       </c>
       <c r="D11" s="52">
         <v>46167</v>
@@ -4290,20 +4290,20 @@
       <c r="CY11" s="32"/>
       <c r="CZ11" s="32"/>
       <c r="DA11" s="32"/>
-      <c r="DB11" s="125"/>
-      <c r="DC11" s="125"/>
-      <c r="DD11" s="125"/>
-      <c r="DE11" s="125"/>
-      <c r="DF11" s="125"/>
-      <c r="DG11" s="125"/>
-      <c r="DH11" s="125"/>
-      <c r="DI11" s="125"/>
-      <c r="DJ11" s="125"/>
-      <c r="DK11" s="125"/>
-      <c r="DL11" s="125"/>
-      <c r="DM11" s="125"/>
-      <c r="DN11" s="125"/>
-      <c r="DO11" s="126"/>
+      <c r="DB11" s="131"/>
+      <c r="DC11" s="131"/>
+      <c r="DD11" s="131"/>
+      <c r="DE11" s="131"/>
+      <c r="DF11" s="131"/>
+      <c r="DG11" s="131"/>
+      <c r="DH11" s="131"/>
+      <c r="DI11" s="131"/>
+      <c r="DJ11" s="131"/>
+      <c r="DK11" s="131"/>
+      <c r="DL11" s="131"/>
+      <c r="DM11" s="131"/>
+      <c r="DN11" s="131"/>
+      <c r="DO11" s="132"/>
       <c r="DP11" s="114"/>
       <c r="DQ11" s="32"/>
       <c r="DR11" s="32"/>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="34">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="D12" s="52">
         <v>46156</v>
@@ -4451,20 +4451,20 @@
       <c r="CY12" s="32"/>
       <c r="CZ12" s="32"/>
       <c r="DA12" s="32"/>
-      <c r="DB12" s="125"/>
-      <c r="DC12" s="125"/>
-      <c r="DD12" s="125"/>
-      <c r="DE12" s="125"/>
-      <c r="DF12" s="125"/>
-      <c r="DG12" s="125"/>
-      <c r="DH12" s="125"/>
-      <c r="DI12" s="125"/>
-      <c r="DJ12" s="125"/>
-      <c r="DK12" s="125"/>
-      <c r="DL12" s="125"/>
-      <c r="DM12" s="125"/>
-      <c r="DN12" s="125"/>
-      <c r="DO12" s="126"/>
+      <c r="DB12" s="131"/>
+      <c r="DC12" s="131"/>
+      <c r="DD12" s="131"/>
+      <c r="DE12" s="131"/>
+      <c r="DF12" s="131"/>
+      <c r="DG12" s="131"/>
+      <c r="DH12" s="131"/>
+      <c r="DI12" s="131"/>
+      <c r="DJ12" s="131"/>
+      <c r="DK12" s="131"/>
+      <c r="DL12" s="131"/>
+      <c r="DM12" s="131"/>
+      <c r="DN12" s="131"/>
+      <c r="DO12" s="132"/>
       <c r="DP12" s="114"/>
       <c r="DQ12" s="32"/>
       <c r="DR12" s="32"/>
@@ -4501,7 +4501,7 @@
         <v>14</v>
       </c>
       <c r="C13" s="34">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D13" s="52">
         <v>46156</v>
@@ -4609,20 +4609,20 @@
       <c r="CY13" s="32"/>
       <c r="CZ13" s="32"/>
       <c r="DA13" s="32"/>
-      <c r="DB13" s="125"/>
-      <c r="DC13" s="125"/>
-      <c r="DD13" s="125"/>
-      <c r="DE13" s="125"/>
-      <c r="DF13" s="125"/>
-      <c r="DG13" s="125"/>
-      <c r="DH13" s="125"/>
-      <c r="DI13" s="125"/>
-      <c r="DJ13" s="125"/>
-      <c r="DK13" s="125"/>
-      <c r="DL13" s="125"/>
-      <c r="DM13" s="125"/>
-      <c r="DN13" s="125"/>
-      <c r="DO13" s="126"/>
+      <c r="DB13" s="131"/>
+      <c r="DC13" s="131"/>
+      <c r="DD13" s="131"/>
+      <c r="DE13" s="131"/>
+      <c r="DF13" s="131"/>
+      <c r="DG13" s="131"/>
+      <c r="DH13" s="131"/>
+      <c r="DI13" s="131"/>
+      <c r="DJ13" s="131"/>
+      <c r="DK13" s="131"/>
+      <c r="DL13" s="131"/>
+      <c r="DM13" s="131"/>
+      <c r="DN13" s="131"/>
+      <c r="DO13" s="132"/>
       <c r="DP13" s="114"/>
       <c r="DQ13" s="32"/>
       <c r="DR13" s="32"/>
@@ -4659,7 +4659,7 @@
         <v>11</v>
       </c>
       <c r="C14" s="34">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D14" s="52">
         <v>46182</v>
@@ -4770,20 +4770,20 @@
       <c r="CY14" s="32"/>
       <c r="CZ14" s="32"/>
       <c r="DA14" s="32"/>
-      <c r="DB14" s="125"/>
-      <c r="DC14" s="125"/>
-      <c r="DD14" s="125"/>
-      <c r="DE14" s="125"/>
-      <c r="DF14" s="125"/>
-      <c r="DG14" s="125"/>
-      <c r="DH14" s="125"/>
-      <c r="DI14" s="125"/>
-      <c r="DJ14" s="125"/>
-      <c r="DK14" s="125"/>
-      <c r="DL14" s="125"/>
-      <c r="DM14" s="125"/>
-      <c r="DN14" s="125"/>
-      <c r="DO14" s="126"/>
+      <c r="DB14" s="131"/>
+      <c r="DC14" s="131"/>
+      <c r="DD14" s="131"/>
+      <c r="DE14" s="131"/>
+      <c r="DF14" s="131"/>
+      <c r="DG14" s="131"/>
+      <c r="DH14" s="131"/>
+      <c r="DI14" s="131"/>
+      <c r="DJ14" s="131"/>
+      <c r="DK14" s="131"/>
+      <c r="DL14" s="131"/>
+      <c r="DM14" s="131"/>
+      <c r="DN14" s="131"/>
+      <c r="DO14" s="132"/>
       <c r="DP14" s="114"/>
       <c r="DQ14" s="32"/>
       <c r="DR14" s="32"/>
@@ -4820,7 +4820,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="34">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D15" s="52">
         <v>46183</v>
@@ -4931,20 +4931,20 @@
       <c r="CY15" s="32"/>
       <c r="CZ15" s="32"/>
       <c r="DA15" s="32"/>
-      <c r="DB15" s="125"/>
-      <c r="DC15" s="125"/>
-      <c r="DD15" s="125"/>
-      <c r="DE15" s="125"/>
-      <c r="DF15" s="125"/>
-      <c r="DG15" s="125"/>
-      <c r="DH15" s="125"/>
-      <c r="DI15" s="125"/>
-      <c r="DJ15" s="125"/>
-      <c r="DK15" s="125"/>
-      <c r="DL15" s="125"/>
-      <c r="DM15" s="125"/>
-      <c r="DN15" s="125"/>
-      <c r="DO15" s="126"/>
+      <c r="DB15" s="131"/>
+      <c r="DC15" s="131"/>
+      <c r="DD15" s="131"/>
+      <c r="DE15" s="131"/>
+      <c r="DF15" s="131"/>
+      <c r="DG15" s="131"/>
+      <c r="DH15" s="131"/>
+      <c r="DI15" s="131"/>
+      <c r="DJ15" s="131"/>
+      <c r="DK15" s="131"/>
+      <c r="DL15" s="131"/>
+      <c r="DM15" s="131"/>
+      <c r="DN15" s="131"/>
+      <c r="DO15" s="132"/>
       <c r="DP15" s="114"/>
       <c r="DQ15" s="32"/>
       <c r="DR15" s="32"/>
@@ -4981,7 +4981,7 @@
         <v>18</v>
       </c>
       <c r="C16" s="34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="52">
         <v>46183</v>
@@ -5092,20 +5092,20 @@
       <c r="CY16" s="32"/>
       <c r="CZ16" s="32"/>
       <c r="DA16" s="32"/>
-      <c r="DB16" s="125"/>
-      <c r="DC16" s="125"/>
-      <c r="DD16" s="125"/>
-      <c r="DE16" s="125"/>
-      <c r="DF16" s="125"/>
-      <c r="DG16" s="125"/>
-      <c r="DH16" s="125"/>
-      <c r="DI16" s="125"/>
-      <c r="DJ16" s="125"/>
-      <c r="DK16" s="125"/>
-      <c r="DL16" s="125"/>
-      <c r="DM16" s="125"/>
-      <c r="DN16" s="125"/>
-      <c r="DO16" s="126"/>
+      <c r="DB16" s="131"/>
+      <c r="DC16" s="131"/>
+      <c r="DD16" s="131"/>
+      <c r="DE16" s="131"/>
+      <c r="DF16" s="131"/>
+      <c r="DG16" s="131"/>
+      <c r="DH16" s="131"/>
+      <c r="DI16" s="131"/>
+      <c r="DJ16" s="131"/>
+      <c r="DK16" s="131"/>
+      <c r="DL16" s="131"/>
+      <c r="DM16" s="131"/>
+      <c r="DN16" s="131"/>
+      <c r="DO16" s="132"/>
       <c r="DP16" s="114"/>
       <c r="DQ16" s="32"/>
       <c r="DR16" s="32"/>
@@ -5149,20 +5149,20 @@
         <f t="shared" si="65"/>
         <v/>
       </c>
-      <c r="DB17" s="125"/>
-      <c r="DC17" s="125"/>
-      <c r="DD17" s="125"/>
-      <c r="DE17" s="125"/>
-      <c r="DF17" s="125"/>
-      <c r="DG17" s="125"/>
-      <c r="DH17" s="125"/>
-      <c r="DI17" s="125"/>
-      <c r="DJ17" s="125"/>
-      <c r="DK17" s="125"/>
-      <c r="DL17" s="125"/>
-      <c r="DM17" s="125"/>
-      <c r="DN17" s="125"/>
-      <c r="DO17" s="126"/>
+      <c r="DB17" s="131"/>
+      <c r="DC17" s="131"/>
+      <c r="DD17" s="131"/>
+      <c r="DE17" s="131"/>
+      <c r="DF17" s="131"/>
+      <c r="DG17" s="131"/>
+      <c r="DH17" s="131"/>
+      <c r="DI17" s="131"/>
+      <c r="DJ17" s="131"/>
+      <c r="DK17" s="131"/>
+      <c r="DL17" s="131"/>
+      <c r="DM17" s="131"/>
+      <c r="DN17" s="131"/>
+      <c r="DO17" s="132"/>
       <c r="EK17" s="113">
         <f t="shared" si="68"/>
         <v>-10</v>
@@ -5178,7 +5178,7 @@
         <v>19</v>
       </c>
       <c r="C18" s="39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" s="55">
         <v>46184</v>
@@ -5289,20 +5289,20 @@
       <c r="CY18" s="32"/>
       <c r="CZ18" s="32"/>
       <c r="DA18" s="32"/>
-      <c r="DB18" s="125"/>
-      <c r="DC18" s="125"/>
-      <c r="DD18" s="125"/>
-      <c r="DE18" s="125"/>
-      <c r="DF18" s="125"/>
-      <c r="DG18" s="125"/>
-      <c r="DH18" s="125"/>
-      <c r="DI18" s="125"/>
-      <c r="DJ18" s="125"/>
-      <c r="DK18" s="125"/>
-      <c r="DL18" s="125"/>
-      <c r="DM18" s="125"/>
-      <c r="DN18" s="125"/>
-      <c r="DO18" s="126"/>
+      <c r="DB18" s="131"/>
+      <c r="DC18" s="131"/>
+      <c r="DD18" s="131"/>
+      <c r="DE18" s="131"/>
+      <c r="DF18" s="131"/>
+      <c r="DG18" s="131"/>
+      <c r="DH18" s="131"/>
+      <c r="DI18" s="131"/>
+      <c r="DJ18" s="131"/>
+      <c r="DK18" s="131"/>
+      <c r="DL18" s="131"/>
+      <c r="DM18" s="131"/>
+      <c r="DN18" s="131"/>
+      <c r="DO18" s="132"/>
       <c r="DP18" s="114"/>
       <c r="DQ18" s="32"/>
       <c r="DR18" s="32"/>
@@ -5339,7 +5339,7 @@
         <v>24</v>
       </c>
       <c r="C19" s="39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" s="55">
         <v>46186</v>
@@ -5450,20 +5450,20 @@
       <c r="CY19" s="32"/>
       <c r="CZ19" s="32"/>
       <c r="DA19" s="32"/>
-      <c r="DB19" s="125"/>
-      <c r="DC19" s="125"/>
-      <c r="DD19" s="125"/>
-      <c r="DE19" s="125"/>
-      <c r="DF19" s="125"/>
-      <c r="DG19" s="125"/>
-      <c r="DH19" s="125"/>
-      <c r="DI19" s="125"/>
-      <c r="DJ19" s="125"/>
-      <c r="DK19" s="125"/>
-      <c r="DL19" s="125"/>
-      <c r="DM19" s="125"/>
-      <c r="DN19" s="125"/>
-      <c r="DO19" s="126"/>
+      <c r="DB19" s="131"/>
+      <c r="DC19" s="131"/>
+      <c r="DD19" s="131"/>
+      <c r="DE19" s="131"/>
+      <c r="DF19" s="131"/>
+      <c r="DG19" s="131"/>
+      <c r="DH19" s="131"/>
+      <c r="DI19" s="131"/>
+      <c r="DJ19" s="131"/>
+      <c r="DK19" s="131"/>
+      <c r="DL19" s="131"/>
+      <c r="DM19" s="131"/>
+      <c r="DN19" s="131"/>
+      <c r="DO19" s="132"/>
       <c r="DP19" s="114"/>
       <c r="DQ19" s="32"/>
       <c r="DR19" s="32"/>
@@ -5500,7 +5500,7 @@
         <v>16</v>
       </c>
       <c r="C20" s="39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" s="55">
         <v>46186</v>
@@ -5608,20 +5608,20 @@
       <c r="CY20" s="32"/>
       <c r="CZ20" s="32"/>
       <c r="DA20" s="32"/>
-      <c r="DB20" s="125"/>
-      <c r="DC20" s="125"/>
-      <c r="DD20" s="125"/>
-      <c r="DE20" s="125"/>
-      <c r="DF20" s="125"/>
-      <c r="DG20" s="125"/>
-      <c r="DH20" s="125"/>
-      <c r="DI20" s="125"/>
-      <c r="DJ20" s="125"/>
-      <c r="DK20" s="125"/>
-      <c r="DL20" s="125"/>
-      <c r="DM20" s="125"/>
-      <c r="DN20" s="125"/>
-      <c r="DO20" s="126"/>
+      <c r="DB20" s="131"/>
+      <c r="DC20" s="131"/>
+      <c r="DD20" s="131"/>
+      <c r="DE20" s="131"/>
+      <c r="DF20" s="131"/>
+      <c r="DG20" s="131"/>
+      <c r="DH20" s="131"/>
+      <c r="DI20" s="131"/>
+      <c r="DJ20" s="131"/>
+      <c r="DK20" s="131"/>
+      <c r="DL20" s="131"/>
+      <c r="DM20" s="131"/>
+      <c r="DN20" s="131"/>
+      <c r="DO20" s="132"/>
       <c r="DP20" s="114"/>
       <c r="DQ20" s="32"/>
       <c r="DR20" s="32"/>
@@ -5763,20 +5763,20 @@
       <c r="CY21" s="42"/>
       <c r="CZ21" s="42"/>
       <c r="DA21" s="42"/>
-      <c r="DB21" s="125"/>
-      <c r="DC21" s="125"/>
-      <c r="DD21" s="125"/>
-      <c r="DE21" s="125"/>
-      <c r="DF21" s="125"/>
-      <c r="DG21" s="125"/>
-      <c r="DH21" s="125"/>
-      <c r="DI21" s="125"/>
-      <c r="DJ21" s="125"/>
-      <c r="DK21" s="125"/>
-      <c r="DL21" s="125"/>
-      <c r="DM21" s="125"/>
-      <c r="DN21" s="125"/>
-      <c r="DO21" s="126"/>
+      <c r="DB21" s="131"/>
+      <c r="DC21" s="131"/>
+      <c r="DD21" s="131"/>
+      <c r="DE21" s="131"/>
+      <c r="DF21" s="131"/>
+      <c r="DG21" s="131"/>
+      <c r="DH21" s="131"/>
+      <c r="DI21" s="131"/>
+      <c r="DJ21" s="131"/>
+      <c r="DK21" s="131"/>
+      <c r="DL21" s="131"/>
+      <c r="DM21" s="131"/>
+      <c r="DN21" s="131"/>
+      <c r="DO21" s="132"/>
       <c r="DP21" s="42"/>
       <c r="DQ21" s="42"/>
       <c r="DR21" s="42"/>
@@ -5813,7 +5813,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" s="58">
         <v>46187</v>
@@ -5924,20 +5924,20 @@
       <c r="CY22" s="32"/>
       <c r="CZ22" s="32"/>
       <c r="DA22" s="32"/>
-      <c r="DB22" s="125"/>
-      <c r="DC22" s="125"/>
-      <c r="DD22" s="125"/>
-      <c r="DE22" s="125"/>
-      <c r="DF22" s="125"/>
-      <c r="DG22" s="125"/>
-      <c r="DH22" s="125"/>
-      <c r="DI22" s="125"/>
-      <c r="DJ22" s="125"/>
-      <c r="DK22" s="125"/>
-      <c r="DL22" s="125"/>
-      <c r="DM22" s="125"/>
-      <c r="DN22" s="125"/>
-      <c r="DO22" s="126"/>
+      <c r="DB22" s="131"/>
+      <c r="DC22" s="131"/>
+      <c r="DD22" s="131"/>
+      <c r="DE22" s="131"/>
+      <c r="DF22" s="131"/>
+      <c r="DG22" s="131"/>
+      <c r="DH22" s="131"/>
+      <c r="DI22" s="131"/>
+      <c r="DJ22" s="131"/>
+      <c r="DK22" s="131"/>
+      <c r="DL22" s="131"/>
+      <c r="DM22" s="131"/>
+      <c r="DN22" s="131"/>
+      <c r="DO22" s="132"/>
       <c r="DP22" s="114"/>
       <c r="DQ22" s="32"/>
       <c r="DR22" s="32"/>
@@ -5974,7 +5974,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" s="58">
         <v>46190</v>
@@ -6085,20 +6085,20 @@
       <c r="CY23" s="32"/>
       <c r="CZ23" s="32"/>
       <c r="DA23" s="32"/>
-      <c r="DB23" s="125"/>
-      <c r="DC23" s="125"/>
-      <c r="DD23" s="125"/>
-      <c r="DE23" s="125"/>
-      <c r="DF23" s="125"/>
-      <c r="DG23" s="125"/>
-      <c r="DH23" s="125"/>
-      <c r="DI23" s="125"/>
-      <c r="DJ23" s="125"/>
-      <c r="DK23" s="125"/>
-      <c r="DL23" s="125"/>
-      <c r="DM23" s="125"/>
-      <c r="DN23" s="125"/>
-      <c r="DO23" s="126"/>
+      <c r="DB23" s="131"/>
+      <c r="DC23" s="131"/>
+      <c r="DD23" s="131"/>
+      <c r="DE23" s="131"/>
+      <c r="DF23" s="131"/>
+      <c r="DG23" s="131"/>
+      <c r="DH23" s="131"/>
+      <c r="DI23" s="131"/>
+      <c r="DJ23" s="131"/>
+      <c r="DK23" s="131"/>
+      <c r="DL23" s="131"/>
+      <c r="DM23" s="131"/>
+      <c r="DN23" s="131"/>
+      <c r="DO23" s="132"/>
       <c r="DP23" s="114"/>
       <c r="DQ23" s="32"/>
       <c r="DR23" s="32"/>
@@ -6240,20 +6240,20 @@
       <c r="CY24" s="47"/>
       <c r="CZ24" s="47"/>
       <c r="DA24" s="47"/>
-      <c r="DB24" s="125"/>
-      <c r="DC24" s="125"/>
-      <c r="DD24" s="125"/>
-      <c r="DE24" s="125"/>
-      <c r="DF24" s="125"/>
-      <c r="DG24" s="125"/>
-      <c r="DH24" s="125"/>
-      <c r="DI24" s="125"/>
-      <c r="DJ24" s="125"/>
-      <c r="DK24" s="125"/>
-      <c r="DL24" s="125"/>
-      <c r="DM24" s="125"/>
-      <c r="DN24" s="125"/>
-      <c r="DO24" s="126"/>
+      <c r="DB24" s="131"/>
+      <c r="DC24" s="131"/>
+      <c r="DD24" s="131"/>
+      <c r="DE24" s="131"/>
+      <c r="DF24" s="131"/>
+      <c r="DG24" s="131"/>
+      <c r="DH24" s="131"/>
+      <c r="DI24" s="131"/>
+      <c r="DJ24" s="131"/>
+      <c r="DK24" s="131"/>
+      <c r="DL24" s="131"/>
+      <c r="DM24" s="131"/>
+      <c r="DN24" s="131"/>
+      <c r="DO24" s="132"/>
       <c r="DP24" s="47"/>
       <c r="DQ24" s="47"/>
       <c r="DR24" s="47"/>
@@ -6290,7 +6290,7 @@
         <v>26</v>
       </c>
       <c r="C25" s="49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" s="61">
         <v>46191</v>
@@ -6401,20 +6401,20 @@
       <c r="CY25" s="32"/>
       <c r="CZ25" s="32"/>
       <c r="DA25" s="32"/>
-      <c r="DB25" s="125"/>
-      <c r="DC25" s="125"/>
-      <c r="DD25" s="125"/>
-      <c r="DE25" s="125"/>
-      <c r="DF25" s="125"/>
-      <c r="DG25" s="125"/>
-      <c r="DH25" s="125"/>
-      <c r="DI25" s="125"/>
-      <c r="DJ25" s="125"/>
-      <c r="DK25" s="125"/>
-      <c r="DL25" s="125"/>
-      <c r="DM25" s="125"/>
-      <c r="DN25" s="125"/>
-      <c r="DO25" s="126"/>
+      <c r="DB25" s="131"/>
+      <c r="DC25" s="131"/>
+      <c r="DD25" s="131"/>
+      <c r="DE25" s="131"/>
+      <c r="DF25" s="131"/>
+      <c r="DG25" s="131"/>
+      <c r="DH25" s="131"/>
+      <c r="DI25" s="131"/>
+      <c r="DJ25" s="131"/>
+      <c r="DK25" s="131"/>
+      <c r="DL25" s="131"/>
+      <c r="DM25" s="131"/>
+      <c r="DN25" s="131"/>
+      <c r="DO25" s="132"/>
       <c r="DP25" s="114"/>
       <c r="DQ25" s="32"/>
       <c r="DR25" s="32"/>
@@ -6451,7 +6451,7 @@
         <v>23</v>
       </c>
       <c r="C26" s="49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" s="61">
         <v>46192</v>
@@ -6562,20 +6562,20 @@
       <c r="CY26" s="32"/>
       <c r="CZ26" s="32"/>
       <c r="DA26" s="32"/>
-      <c r="DB26" s="125"/>
-      <c r="DC26" s="125"/>
-      <c r="DD26" s="125"/>
-      <c r="DE26" s="125"/>
-      <c r="DF26" s="125"/>
-      <c r="DG26" s="125"/>
-      <c r="DH26" s="125"/>
-      <c r="DI26" s="125"/>
-      <c r="DJ26" s="125"/>
-      <c r="DK26" s="125"/>
-      <c r="DL26" s="125"/>
-      <c r="DM26" s="125"/>
-      <c r="DN26" s="125"/>
-      <c r="DO26" s="126"/>
+      <c r="DB26" s="131"/>
+      <c r="DC26" s="131"/>
+      <c r="DD26" s="131"/>
+      <c r="DE26" s="131"/>
+      <c r="DF26" s="131"/>
+      <c r="DG26" s="131"/>
+      <c r="DH26" s="131"/>
+      <c r="DI26" s="131"/>
+      <c r="DJ26" s="131"/>
+      <c r="DK26" s="131"/>
+      <c r="DL26" s="131"/>
+      <c r="DM26" s="131"/>
+      <c r="DN26" s="131"/>
+      <c r="DO26" s="132"/>
       <c r="DP26" s="114"/>
       <c r="DQ26" s="32"/>
       <c r="DR26" s="32"/>
@@ -6723,20 +6723,20 @@
       <c r="CY27" s="32"/>
       <c r="CZ27" s="32"/>
       <c r="DA27" s="32"/>
-      <c r="DB27" s="125"/>
-      <c r="DC27" s="125"/>
-      <c r="DD27" s="125"/>
-      <c r="DE27" s="125"/>
-      <c r="DF27" s="125"/>
-      <c r="DG27" s="125"/>
-      <c r="DH27" s="125"/>
-      <c r="DI27" s="125"/>
-      <c r="DJ27" s="125"/>
-      <c r="DK27" s="125"/>
-      <c r="DL27" s="125"/>
-      <c r="DM27" s="125"/>
-      <c r="DN27" s="125"/>
-      <c r="DO27" s="126"/>
+      <c r="DB27" s="131"/>
+      <c r="DC27" s="131"/>
+      <c r="DD27" s="131"/>
+      <c r="DE27" s="131"/>
+      <c r="DF27" s="131"/>
+      <c r="DG27" s="131"/>
+      <c r="DH27" s="131"/>
+      <c r="DI27" s="131"/>
+      <c r="DJ27" s="131"/>
+      <c r="DK27" s="131"/>
+      <c r="DL27" s="131"/>
+      <c r="DM27" s="131"/>
+      <c r="DN27" s="131"/>
+      <c r="DO27" s="132"/>
       <c r="DP27" s="114"/>
       <c r="DQ27" s="32"/>
       <c r="DR27" s="32"/>
@@ -6773,7 +6773,7 @@
         <v>25</v>
       </c>
       <c r="C28" s="71">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="D28" s="72">
         <v>46199</v>
@@ -6884,20 +6884,20 @@
       <c r="CY28" s="32"/>
       <c r="CZ28" s="32"/>
       <c r="DA28" s="32"/>
-      <c r="DB28" s="125"/>
-      <c r="DC28" s="125"/>
-      <c r="DD28" s="125"/>
-      <c r="DE28" s="125"/>
-      <c r="DF28" s="125"/>
-      <c r="DG28" s="125"/>
-      <c r="DH28" s="125"/>
-      <c r="DI28" s="125"/>
-      <c r="DJ28" s="125"/>
-      <c r="DK28" s="125"/>
-      <c r="DL28" s="125"/>
-      <c r="DM28" s="125"/>
-      <c r="DN28" s="125"/>
-      <c r="DO28" s="126"/>
+      <c r="DB28" s="131"/>
+      <c r="DC28" s="131"/>
+      <c r="DD28" s="131"/>
+      <c r="DE28" s="131"/>
+      <c r="DF28" s="131"/>
+      <c r="DG28" s="131"/>
+      <c r="DH28" s="131"/>
+      <c r="DI28" s="131"/>
+      <c r="DJ28" s="131"/>
+      <c r="DK28" s="131"/>
+      <c r="DL28" s="131"/>
+      <c r="DM28" s="131"/>
+      <c r="DN28" s="131"/>
+      <c r="DO28" s="132"/>
       <c r="DP28" s="114"/>
       <c r="DQ28" s="32"/>
       <c r="DR28" s="32"/>
@@ -7039,20 +7039,20 @@
       <c r="CY29" s="47"/>
       <c r="CZ29" s="47"/>
       <c r="DA29" s="47"/>
-      <c r="DB29" s="125"/>
-      <c r="DC29" s="125"/>
-      <c r="DD29" s="125"/>
-      <c r="DE29" s="125"/>
-      <c r="DF29" s="125"/>
-      <c r="DG29" s="125"/>
-      <c r="DH29" s="125"/>
-      <c r="DI29" s="125"/>
-      <c r="DJ29" s="125"/>
-      <c r="DK29" s="125"/>
-      <c r="DL29" s="125"/>
-      <c r="DM29" s="125"/>
-      <c r="DN29" s="125"/>
-      <c r="DO29" s="126"/>
+      <c r="DB29" s="131"/>
+      <c r="DC29" s="131"/>
+      <c r="DD29" s="131"/>
+      <c r="DE29" s="131"/>
+      <c r="DF29" s="131"/>
+      <c r="DG29" s="131"/>
+      <c r="DH29" s="131"/>
+      <c r="DI29" s="131"/>
+      <c r="DJ29" s="131"/>
+      <c r="DK29" s="131"/>
+      <c r="DL29" s="131"/>
+      <c r="DM29" s="131"/>
+      <c r="DN29" s="131"/>
+      <c r="DO29" s="132"/>
       <c r="DP29" s="47"/>
       <c r="DQ29" s="47"/>
       <c r="DR29" s="47"/>
@@ -7089,7 +7089,7 @@
         <v>28</v>
       </c>
       <c r="C30" s="82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" s="83">
         <v>46200</v>
@@ -7200,20 +7200,20 @@
       <c r="CY30" s="32"/>
       <c r="CZ30" s="32"/>
       <c r="DA30" s="32"/>
-      <c r="DB30" s="125"/>
-      <c r="DC30" s="125"/>
-      <c r="DD30" s="125"/>
-      <c r="DE30" s="125"/>
-      <c r="DF30" s="125"/>
-      <c r="DG30" s="125"/>
-      <c r="DH30" s="125"/>
-      <c r="DI30" s="125"/>
-      <c r="DJ30" s="125"/>
-      <c r="DK30" s="125"/>
-      <c r="DL30" s="125"/>
-      <c r="DM30" s="125"/>
-      <c r="DN30" s="125"/>
-      <c r="DO30" s="126"/>
+      <c r="DB30" s="131"/>
+      <c r="DC30" s="131"/>
+      <c r="DD30" s="131"/>
+      <c r="DE30" s="131"/>
+      <c r="DF30" s="131"/>
+      <c r="DG30" s="131"/>
+      <c r="DH30" s="131"/>
+      <c r="DI30" s="131"/>
+      <c r="DJ30" s="131"/>
+      <c r="DK30" s="131"/>
+      <c r="DL30" s="131"/>
+      <c r="DM30" s="131"/>
+      <c r="DN30" s="131"/>
+      <c r="DO30" s="132"/>
       <c r="DP30" s="114"/>
       <c r="DQ30" s="32"/>
       <c r="DR30" s="32"/>
@@ -7250,7 +7250,7 @@
         <v>29</v>
       </c>
       <c r="C31" s="86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31" s="87">
         <v>46205</v>
@@ -7361,20 +7361,20 @@
       <c r="CY31" s="32"/>
       <c r="CZ31" s="32"/>
       <c r="DA31" s="32"/>
-      <c r="DB31" s="125"/>
-      <c r="DC31" s="125"/>
-      <c r="DD31" s="125"/>
-      <c r="DE31" s="125"/>
-      <c r="DF31" s="125"/>
-      <c r="DG31" s="125"/>
-      <c r="DH31" s="125"/>
-      <c r="DI31" s="125"/>
-      <c r="DJ31" s="125"/>
-      <c r="DK31" s="125"/>
-      <c r="DL31" s="125"/>
-      <c r="DM31" s="125"/>
-      <c r="DN31" s="125"/>
-      <c r="DO31" s="126"/>
+      <c r="DB31" s="131"/>
+      <c r="DC31" s="131"/>
+      <c r="DD31" s="131"/>
+      <c r="DE31" s="131"/>
+      <c r="DF31" s="131"/>
+      <c r="DG31" s="131"/>
+      <c r="DH31" s="131"/>
+      <c r="DI31" s="131"/>
+      <c r="DJ31" s="131"/>
+      <c r="DK31" s="131"/>
+      <c r="DL31" s="131"/>
+      <c r="DM31" s="131"/>
+      <c r="DN31" s="131"/>
+      <c r="DO31" s="132"/>
       <c r="DP31" s="114"/>
       <c r="DQ31" s="32"/>
       <c r="DR31" s="32"/>
@@ -7411,7 +7411,7 @@
         <v>30</v>
       </c>
       <c r="C32" s="82">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="D32" s="83">
         <v>46208</v>
@@ -7522,20 +7522,20 @@
       <c r="CY32" s="32"/>
       <c r="CZ32" s="32"/>
       <c r="DA32" s="32"/>
-      <c r="DB32" s="125"/>
-      <c r="DC32" s="125"/>
-      <c r="DD32" s="125"/>
-      <c r="DE32" s="125"/>
-      <c r="DF32" s="125"/>
-      <c r="DG32" s="125"/>
-      <c r="DH32" s="125"/>
-      <c r="DI32" s="125"/>
-      <c r="DJ32" s="125"/>
-      <c r="DK32" s="125"/>
-      <c r="DL32" s="125"/>
-      <c r="DM32" s="125"/>
-      <c r="DN32" s="125"/>
-      <c r="DO32" s="126"/>
+      <c r="DB32" s="131"/>
+      <c r="DC32" s="131"/>
+      <c r="DD32" s="131"/>
+      <c r="DE32" s="131"/>
+      <c r="DF32" s="131"/>
+      <c r="DG32" s="131"/>
+      <c r="DH32" s="131"/>
+      <c r="DI32" s="131"/>
+      <c r="DJ32" s="131"/>
+      <c r="DK32" s="131"/>
+      <c r="DL32" s="131"/>
+      <c r="DM32" s="131"/>
+      <c r="DN32" s="131"/>
+      <c r="DO32" s="132"/>
       <c r="DP32" s="114"/>
       <c r="DQ32" s="32"/>
       <c r="DR32" s="32"/>
@@ -7572,7 +7572,7 @@
         <v>31</v>
       </c>
       <c r="C33" s="78">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="D33" s="79">
         <v>46212</v>
@@ -7683,20 +7683,20 @@
       <c r="CY33" s="32"/>
       <c r="CZ33" s="32"/>
       <c r="DA33" s="32"/>
-      <c r="DB33" s="125"/>
-      <c r="DC33" s="125"/>
-      <c r="DD33" s="125"/>
-      <c r="DE33" s="125"/>
-      <c r="DF33" s="125"/>
-      <c r="DG33" s="125"/>
-      <c r="DH33" s="125"/>
-      <c r="DI33" s="125"/>
-      <c r="DJ33" s="125"/>
-      <c r="DK33" s="125"/>
-      <c r="DL33" s="125"/>
-      <c r="DM33" s="125"/>
-      <c r="DN33" s="125"/>
-      <c r="DO33" s="126"/>
+      <c r="DB33" s="131"/>
+      <c r="DC33" s="131"/>
+      <c r="DD33" s="131"/>
+      <c r="DE33" s="131"/>
+      <c r="DF33" s="131"/>
+      <c r="DG33" s="131"/>
+      <c r="DH33" s="131"/>
+      <c r="DI33" s="131"/>
+      <c r="DJ33" s="131"/>
+      <c r="DK33" s="131"/>
+      <c r="DL33" s="131"/>
+      <c r="DM33" s="131"/>
+      <c r="DN33" s="131"/>
+      <c r="DO33" s="132"/>
       <c r="DP33" s="114"/>
       <c r="DQ33" s="32"/>
       <c r="DR33" s="32"/>
@@ -7838,20 +7838,20 @@
       <c r="CY34" s="47"/>
       <c r="CZ34" s="47"/>
       <c r="DA34" s="47"/>
-      <c r="DB34" s="125"/>
-      <c r="DC34" s="125"/>
-      <c r="DD34" s="125"/>
-      <c r="DE34" s="125"/>
-      <c r="DF34" s="125"/>
-      <c r="DG34" s="125"/>
-      <c r="DH34" s="125"/>
-      <c r="DI34" s="125"/>
-      <c r="DJ34" s="125"/>
-      <c r="DK34" s="125"/>
-      <c r="DL34" s="125"/>
-      <c r="DM34" s="125"/>
-      <c r="DN34" s="125"/>
-      <c r="DO34" s="126"/>
+      <c r="DB34" s="131"/>
+      <c r="DC34" s="131"/>
+      <c r="DD34" s="131"/>
+      <c r="DE34" s="131"/>
+      <c r="DF34" s="131"/>
+      <c r="DG34" s="131"/>
+      <c r="DH34" s="131"/>
+      <c r="DI34" s="131"/>
+      <c r="DJ34" s="131"/>
+      <c r="DK34" s="131"/>
+      <c r="DL34" s="131"/>
+      <c r="DM34" s="131"/>
+      <c r="DN34" s="131"/>
+      <c r="DO34" s="132"/>
       <c r="DP34" s="47"/>
       <c r="DQ34" s="47"/>
       <c r="DR34" s="47"/>
@@ -7888,7 +7888,7 @@
         <v>33</v>
       </c>
       <c r="C35" s="95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35" s="96">
         <v>46213</v>
@@ -7999,20 +7999,20 @@
       <c r="CY35" s="32"/>
       <c r="CZ35" s="32"/>
       <c r="DA35" s="32"/>
-      <c r="DB35" s="125"/>
-      <c r="DC35" s="125"/>
-      <c r="DD35" s="125"/>
-      <c r="DE35" s="125"/>
-      <c r="DF35" s="125"/>
-      <c r="DG35" s="125"/>
-      <c r="DH35" s="125"/>
-      <c r="DI35" s="125"/>
-      <c r="DJ35" s="125"/>
-      <c r="DK35" s="125"/>
-      <c r="DL35" s="125"/>
-      <c r="DM35" s="125"/>
-      <c r="DN35" s="125"/>
-      <c r="DO35" s="126"/>
+      <c r="DB35" s="131"/>
+      <c r="DC35" s="131"/>
+      <c r="DD35" s="131"/>
+      <c r="DE35" s="131"/>
+      <c r="DF35" s="131"/>
+      <c r="DG35" s="131"/>
+      <c r="DH35" s="131"/>
+      <c r="DI35" s="131"/>
+      <c r="DJ35" s="131"/>
+      <c r="DK35" s="131"/>
+      <c r="DL35" s="131"/>
+      <c r="DM35" s="131"/>
+      <c r="DN35" s="131"/>
+      <c r="DO35" s="132"/>
       <c r="DP35" s="114"/>
       <c r="DQ35" s="32"/>
       <c r="DR35" s="32"/>
@@ -8049,7 +8049,7 @@
         <v>34</v>
       </c>
       <c r="C36" s="99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36" s="100">
         <v>46218</v>
@@ -8160,20 +8160,20 @@
       <c r="CY36" s="32"/>
       <c r="CZ36" s="32"/>
       <c r="DA36" s="32"/>
-      <c r="DB36" s="125"/>
-      <c r="DC36" s="125"/>
-      <c r="DD36" s="125"/>
-      <c r="DE36" s="125"/>
-      <c r="DF36" s="125"/>
-      <c r="DG36" s="125"/>
-      <c r="DH36" s="125"/>
-      <c r="DI36" s="125"/>
-      <c r="DJ36" s="125"/>
-      <c r="DK36" s="125"/>
-      <c r="DL36" s="125"/>
-      <c r="DM36" s="125"/>
-      <c r="DN36" s="125"/>
-      <c r="DO36" s="126"/>
+      <c r="DB36" s="131"/>
+      <c r="DC36" s="131"/>
+      <c r="DD36" s="131"/>
+      <c r="DE36" s="131"/>
+      <c r="DF36" s="131"/>
+      <c r="DG36" s="131"/>
+      <c r="DH36" s="131"/>
+      <c r="DI36" s="131"/>
+      <c r="DJ36" s="131"/>
+      <c r="DK36" s="131"/>
+      <c r="DL36" s="131"/>
+      <c r="DM36" s="131"/>
+      <c r="DN36" s="131"/>
+      <c r="DO36" s="132"/>
       <c r="DP36" s="114"/>
       <c r="DQ36" s="32"/>
       <c r="DR36" s="32"/>
@@ -8321,20 +8321,20 @@
       <c r="CY37" s="32"/>
       <c r="CZ37" s="32"/>
       <c r="DA37" s="32"/>
-      <c r="DB37" s="125"/>
-      <c r="DC37" s="125"/>
-      <c r="DD37" s="125"/>
-      <c r="DE37" s="125"/>
-      <c r="DF37" s="125"/>
-      <c r="DG37" s="125"/>
-      <c r="DH37" s="125"/>
-      <c r="DI37" s="125"/>
-      <c r="DJ37" s="125"/>
-      <c r="DK37" s="125"/>
-      <c r="DL37" s="125"/>
-      <c r="DM37" s="125"/>
-      <c r="DN37" s="125"/>
-      <c r="DO37" s="126"/>
+      <c r="DB37" s="131"/>
+      <c r="DC37" s="131"/>
+      <c r="DD37" s="131"/>
+      <c r="DE37" s="131"/>
+      <c r="DF37" s="131"/>
+      <c r="DG37" s="131"/>
+      <c r="DH37" s="131"/>
+      <c r="DI37" s="131"/>
+      <c r="DJ37" s="131"/>
+      <c r="DK37" s="131"/>
+      <c r="DL37" s="131"/>
+      <c r="DM37" s="131"/>
+      <c r="DN37" s="131"/>
+      <c r="DO37" s="132"/>
       <c r="DP37" s="114"/>
       <c r="DQ37" s="32"/>
       <c r="DR37" s="32"/>
@@ -8371,7 +8371,7 @@
         <v>36</v>
       </c>
       <c r="C38" s="104">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="D38" s="100">
         <v>46221</v>
@@ -8482,20 +8482,20 @@
       <c r="CY38" s="32"/>
       <c r="CZ38" s="32"/>
       <c r="DA38" s="32"/>
-      <c r="DB38" s="125"/>
-      <c r="DC38" s="125"/>
-      <c r="DD38" s="125"/>
-      <c r="DE38" s="125"/>
-      <c r="DF38" s="125"/>
-      <c r="DG38" s="125"/>
-      <c r="DH38" s="125"/>
-      <c r="DI38" s="125"/>
-      <c r="DJ38" s="125"/>
-      <c r="DK38" s="125"/>
-      <c r="DL38" s="125"/>
-      <c r="DM38" s="125"/>
-      <c r="DN38" s="125"/>
-      <c r="DO38" s="126"/>
+      <c r="DB38" s="131"/>
+      <c r="DC38" s="131"/>
+      <c r="DD38" s="131"/>
+      <c r="DE38" s="131"/>
+      <c r="DF38" s="131"/>
+      <c r="DG38" s="131"/>
+      <c r="DH38" s="131"/>
+      <c r="DI38" s="131"/>
+      <c r="DJ38" s="131"/>
+      <c r="DK38" s="131"/>
+      <c r="DL38" s="131"/>
+      <c r="DM38" s="131"/>
+      <c r="DN38" s="131"/>
+      <c r="DO38" s="132"/>
       <c r="DP38" s="114"/>
       <c r="DQ38" s="32"/>
       <c r="DR38" s="32"/>
@@ -8643,20 +8643,20 @@
       <c r="CY39" s="32"/>
       <c r="CZ39" s="32"/>
       <c r="DA39" s="32"/>
-      <c r="DB39" s="125"/>
-      <c r="DC39" s="125"/>
-      <c r="DD39" s="125"/>
-      <c r="DE39" s="125"/>
-      <c r="DF39" s="125"/>
-      <c r="DG39" s="125"/>
-      <c r="DH39" s="125"/>
-      <c r="DI39" s="125"/>
-      <c r="DJ39" s="125"/>
-      <c r="DK39" s="125"/>
-      <c r="DL39" s="125"/>
-      <c r="DM39" s="125"/>
-      <c r="DN39" s="125"/>
-      <c r="DO39" s="126"/>
+      <c r="DB39" s="131"/>
+      <c r="DC39" s="131"/>
+      <c r="DD39" s="131"/>
+      <c r="DE39" s="131"/>
+      <c r="DF39" s="131"/>
+      <c r="DG39" s="131"/>
+      <c r="DH39" s="131"/>
+      <c r="DI39" s="131"/>
+      <c r="DJ39" s="131"/>
+      <c r="DK39" s="131"/>
+      <c r="DL39" s="131"/>
+      <c r="DM39" s="131"/>
+      <c r="DN39" s="131"/>
+      <c r="DO39" s="132"/>
       <c r="DP39" s="114"/>
       <c r="DQ39" s="32"/>
       <c r="DR39" s="32"/>
@@ -8798,20 +8798,20 @@
       <c r="CY40" s="28"/>
       <c r="CZ40" s="28"/>
       <c r="DA40" s="28"/>
-      <c r="DB40" s="125"/>
-      <c r="DC40" s="125"/>
-      <c r="DD40" s="125"/>
-      <c r="DE40" s="125"/>
-      <c r="DF40" s="125"/>
-      <c r="DG40" s="125"/>
-      <c r="DH40" s="125"/>
-      <c r="DI40" s="125"/>
-      <c r="DJ40" s="125"/>
-      <c r="DK40" s="125"/>
-      <c r="DL40" s="125"/>
-      <c r="DM40" s="125"/>
-      <c r="DN40" s="125"/>
-      <c r="DO40" s="126"/>
+      <c r="DB40" s="131"/>
+      <c r="DC40" s="131"/>
+      <c r="DD40" s="131"/>
+      <c r="DE40" s="131"/>
+      <c r="DF40" s="131"/>
+      <c r="DG40" s="131"/>
+      <c r="DH40" s="131"/>
+      <c r="DI40" s="131"/>
+      <c r="DJ40" s="131"/>
+      <c r="DK40" s="131"/>
+      <c r="DL40" s="131"/>
+      <c r="DM40" s="131"/>
+      <c r="DN40" s="131"/>
+      <c r="DO40" s="132"/>
       <c r="DP40" s="28"/>
       <c r="DQ40" s="28"/>
       <c r="DR40" s="28"/>
@@ -8959,20 +8959,20 @@
       <c r="CY41" s="32"/>
       <c r="CZ41" s="32"/>
       <c r="DA41" s="32"/>
-      <c r="DB41" s="125"/>
-      <c r="DC41" s="125"/>
-      <c r="DD41" s="125"/>
-      <c r="DE41" s="125"/>
-      <c r="DF41" s="125"/>
-      <c r="DG41" s="125"/>
-      <c r="DH41" s="125"/>
-      <c r="DI41" s="125"/>
-      <c r="DJ41" s="125"/>
-      <c r="DK41" s="125"/>
-      <c r="DL41" s="125"/>
-      <c r="DM41" s="125"/>
-      <c r="DN41" s="125"/>
-      <c r="DO41" s="126"/>
+      <c r="DB41" s="131"/>
+      <c r="DC41" s="131"/>
+      <c r="DD41" s="131"/>
+      <c r="DE41" s="131"/>
+      <c r="DF41" s="131"/>
+      <c r="DG41" s="131"/>
+      <c r="DH41" s="131"/>
+      <c r="DI41" s="131"/>
+      <c r="DJ41" s="131"/>
+      <c r="DK41" s="131"/>
+      <c r="DL41" s="131"/>
+      <c r="DM41" s="131"/>
+      <c r="DN41" s="131"/>
+      <c r="DO41" s="132"/>
       <c r="DP41" s="114"/>
       <c r="DQ41" s="32"/>
       <c r="DR41" s="32"/>
@@ -9120,20 +9120,20 @@
       <c r="CY42" s="32"/>
       <c r="CZ42" s="32"/>
       <c r="DA42" s="32"/>
-      <c r="DB42" s="125"/>
-      <c r="DC42" s="125"/>
-      <c r="DD42" s="125"/>
-      <c r="DE42" s="125"/>
-      <c r="DF42" s="125"/>
-      <c r="DG42" s="125"/>
-      <c r="DH42" s="125"/>
-      <c r="DI42" s="125"/>
-      <c r="DJ42" s="125"/>
-      <c r="DK42" s="125"/>
-      <c r="DL42" s="125"/>
-      <c r="DM42" s="125"/>
-      <c r="DN42" s="125"/>
-      <c r="DO42" s="126"/>
+      <c r="DB42" s="131"/>
+      <c r="DC42" s="131"/>
+      <c r="DD42" s="131"/>
+      <c r="DE42" s="131"/>
+      <c r="DF42" s="131"/>
+      <c r="DG42" s="131"/>
+      <c r="DH42" s="131"/>
+      <c r="DI42" s="131"/>
+      <c r="DJ42" s="131"/>
+      <c r="DK42" s="131"/>
+      <c r="DL42" s="131"/>
+      <c r="DM42" s="131"/>
+      <c r="DN42" s="131"/>
+      <c r="DO42" s="132"/>
       <c r="DP42" s="114"/>
       <c r="DQ42" s="32"/>
       <c r="DR42" s="32"/>
@@ -9281,20 +9281,20 @@
       <c r="CY43" s="32"/>
       <c r="CZ43" s="32"/>
       <c r="DA43" s="32"/>
-      <c r="DB43" s="125"/>
-      <c r="DC43" s="125"/>
-      <c r="DD43" s="125"/>
-      <c r="DE43" s="125"/>
-      <c r="DF43" s="125"/>
-      <c r="DG43" s="125"/>
-      <c r="DH43" s="125"/>
-      <c r="DI43" s="125"/>
-      <c r="DJ43" s="125"/>
-      <c r="DK43" s="125"/>
-      <c r="DL43" s="125"/>
-      <c r="DM43" s="125"/>
-      <c r="DN43" s="125"/>
-      <c r="DO43" s="126"/>
+      <c r="DB43" s="131"/>
+      <c r="DC43" s="131"/>
+      <c r="DD43" s="131"/>
+      <c r="DE43" s="131"/>
+      <c r="DF43" s="131"/>
+      <c r="DG43" s="131"/>
+      <c r="DH43" s="131"/>
+      <c r="DI43" s="131"/>
+      <c r="DJ43" s="131"/>
+      <c r="DK43" s="131"/>
+      <c r="DL43" s="131"/>
+      <c r="DM43" s="131"/>
+      <c r="DN43" s="131"/>
+      <c r="DO43" s="132"/>
       <c r="DP43" s="114"/>
       <c r="DQ43" s="32"/>
       <c r="DR43" s="32"/>
@@ -9439,20 +9439,20 @@
       <c r="CY44" s="32"/>
       <c r="CZ44" s="32"/>
       <c r="DA44" s="32"/>
-      <c r="DB44" s="125"/>
-      <c r="DC44" s="125"/>
-      <c r="DD44" s="125"/>
-      <c r="DE44" s="125"/>
-      <c r="DF44" s="125"/>
-      <c r="DG44" s="125"/>
-      <c r="DH44" s="125"/>
-      <c r="DI44" s="125"/>
-      <c r="DJ44" s="125"/>
-      <c r="DK44" s="125"/>
-      <c r="DL44" s="125"/>
-      <c r="DM44" s="125"/>
-      <c r="DN44" s="125"/>
-      <c r="DO44" s="126"/>
+      <c r="DB44" s="131"/>
+      <c r="DC44" s="131"/>
+      <c r="DD44" s="131"/>
+      <c r="DE44" s="131"/>
+      <c r="DF44" s="131"/>
+      <c r="DG44" s="131"/>
+      <c r="DH44" s="131"/>
+      <c r="DI44" s="131"/>
+      <c r="DJ44" s="131"/>
+      <c r="DK44" s="131"/>
+      <c r="DL44" s="131"/>
+      <c r="DM44" s="131"/>
+      <c r="DN44" s="131"/>
+      <c r="DO44" s="132"/>
       <c r="DP44" s="114"/>
       <c r="DQ44" s="32"/>
       <c r="DR44" s="32"/>
@@ -9496,20 +9496,20 @@
         <f t="shared" si="65"/>
         <v/>
       </c>
-      <c r="DB45" s="125"/>
-      <c r="DC45" s="125"/>
-      <c r="DD45" s="125"/>
-      <c r="DE45" s="125"/>
-      <c r="DF45" s="125"/>
-      <c r="DG45" s="125"/>
-      <c r="DH45" s="125"/>
-      <c r="DI45" s="125"/>
-      <c r="DJ45" s="125"/>
-      <c r="DK45" s="125"/>
-      <c r="DL45" s="125"/>
-      <c r="DM45" s="125"/>
-      <c r="DN45" s="125"/>
-      <c r="DO45" s="126"/>
+      <c r="DB45" s="131"/>
+      <c r="DC45" s="131"/>
+      <c r="DD45" s="131"/>
+      <c r="DE45" s="131"/>
+      <c r="DF45" s="131"/>
+      <c r="DG45" s="131"/>
+      <c r="DH45" s="131"/>
+      <c r="DI45" s="131"/>
+      <c r="DJ45" s="131"/>
+      <c r="DK45" s="131"/>
+      <c r="DL45" s="131"/>
+      <c r="DM45" s="131"/>
+      <c r="DN45" s="131"/>
+      <c r="DO45" s="132"/>
       <c r="EK45" s="113">
         <f t="shared" si="72"/>
         <v>2</v>
@@ -9636,20 +9636,20 @@
       <c r="CY46" s="32"/>
       <c r="CZ46" s="32"/>
       <c r="DA46" s="32"/>
-      <c r="DB46" s="125"/>
-      <c r="DC46" s="125"/>
-      <c r="DD46" s="125"/>
-      <c r="DE46" s="125"/>
-      <c r="DF46" s="125"/>
-      <c r="DG46" s="125"/>
-      <c r="DH46" s="125"/>
-      <c r="DI46" s="125"/>
-      <c r="DJ46" s="125"/>
-      <c r="DK46" s="125"/>
-      <c r="DL46" s="125"/>
-      <c r="DM46" s="125"/>
-      <c r="DN46" s="125"/>
-      <c r="DO46" s="126"/>
+      <c r="DB46" s="131"/>
+      <c r="DC46" s="131"/>
+      <c r="DD46" s="131"/>
+      <c r="DE46" s="131"/>
+      <c r="DF46" s="131"/>
+      <c r="DG46" s="131"/>
+      <c r="DH46" s="131"/>
+      <c r="DI46" s="131"/>
+      <c r="DJ46" s="131"/>
+      <c r="DK46" s="131"/>
+      <c r="DL46" s="131"/>
+      <c r="DM46" s="131"/>
+      <c r="DN46" s="131"/>
+      <c r="DO46" s="132"/>
       <c r="DP46" s="114"/>
       <c r="DQ46" s="32"/>
       <c r="DR46" s="32"/>
@@ -9797,20 +9797,20 @@
       <c r="CY47" s="32"/>
       <c r="CZ47" s="32"/>
       <c r="DA47" s="32"/>
-      <c r="DB47" s="125"/>
-      <c r="DC47" s="125"/>
-      <c r="DD47" s="125"/>
-      <c r="DE47" s="125"/>
-      <c r="DF47" s="125"/>
-      <c r="DG47" s="125"/>
-      <c r="DH47" s="125"/>
-      <c r="DI47" s="125"/>
-      <c r="DJ47" s="125"/>
-      <c r="DK47" s="125"/>
-      <c r="DL47" s="125"/>
-      <c r="DM47" s="125"/>
-      <c r="DN47" s="125"/>
-      <c r="DO47" s="126"/>
+      <c r="DB47" s="131"/>
+      <c r="DC47" s="131"/>
+      <c r="DD47" s="131"/>
+      <c r="DE47" s="131"/>
+      <c r="DF47" s="131"/>
+      <c r="DG47" s="131"/>
+      <c r="DH47" s="131"/>
+      <c r="DI47" s="131"/>
+      <c r="DJ47" s="131"/>
+      <c r="DK47" s="131"/>
+      <c r="DL47" s="131"/>
+      <c r="DM47" s="131"/>
+      <c r="DN47" s="131"/>
+      <c r="DO47" s="132"/>
       <c r="DP47" s="114"/>
       <c r="DQ47" s="32"/>
       <c r="DR47" s="32"/>
@@ -9953,20 +9953,20 @@
       <c r="CY48" s="32"/>
       <c r="CZ48" s="32"/>
       <c r="DA48" s="32"/>
-      <c r="DB48" s="125"/>
-      <c r="DC48" s="125"/>
-      <c r="DD48" s="125"/>
-      <c r="DE48" s="125"/>
-      <c r="DF48" s="125"/>
-      <c r="DG48" s="125"/>
-      <c r="DH48" s="125"/>
-      <c r="DI48" s="125"/>
-      <c r="DJ48" s="125"/>
-      <c r="DK48" s="125"/>
-      <c r="DL48" s="125"/>
-      <c r="DM48" s="125"/>
-      <c r="DN48" s="125"/>
-      <c r="DO48" s="126"/>
+      <c r="DB48" s="131"/>
+      <c r="DC48" s="131"/>
+      <c r="DD48" s="131"/>
+      <c r="DE48" s="131"/>
+      <c r="DF48" s="131"/>
+      <c r="DG48" s="131"/>
+      <c r="DH48" s="131"/>
+      <c r="DI48" s="131"/>
+      <c r="DJ48" s="131"/>
+      <c r="DK48" s="131"/>
+      <c r="DL48" s="131"/>
+      <c r="DM48" s="131"/>
+      <c r="DN48" s="131"/>
+      <c r="DO48" s="132"/>
       <c r="DP48" s="114"/>
       <c r="DQ48" s="32"/>
       <c r="DR48" s="32"/>
@@ -10109,20 +10109,20 @@
       <c r="CY49" s="32"/>
       <c r="CZ49" s="32"/>
       <c r="DA49" s="32"/>
-      <c r="DB49" s="125"/>
-      <c r="DC49" s="125"/>
-      <c r="DD49" s="125"/>
-      <c r="DE49" s="125"/>
-      <c r="DF49" s="125"/>
-      <c r="DG49" s="125"/>
-      <c r="DH49" s="125"/>
-      <c r="DI49" s="125"/>
-      <c r="DJ49" s="125"/>
-      <c r="DK49" s="125"/>
-      <c r="DL49" s="125"/>
-      <c r="DM49" s="125"/>
-      <c r="DN49" s="125"/>
-      <c r="DO49" s="126"/>
+      <c r="DB49" s="131"/>
+      <c r="DC49" s="131"/>
+      <c r="DD49" s="131"/>
+      <c r="DE49" s="131"/>
+      <c r="DF49" s="131"/>
+      <c r="DG49" s="131"/>
+      <c r="DH49" s="131"/>
+      <c r="DI49" s="131"/>
+      <c r="DJ49" s="131"/>
+      <c r="DK49" s="131"/>
+      <c r="DL49" s="131"/>
+      <c r="DM49" s="131"/>
+      <c r="DN49" s="131"/>
+      <c r="DO49" s="132"/>
       <c r="DP49" s="114"/>
       <c r="DQ49" s="32"/>
       <c r="DR49" s="32"/>
@@ -10265,20 +10265,20 @@
       <c r="CY50" s="32"/>
       <c r="CZ50" s="32"/>
       <c r="DA50" s="32"/>
-      <c r="DB50" s="125"/>
-      <c r="DC50" s="125"/>
-      <c r="DD50" s="125"/>
-      <c r="DE50" s="125"/>
-      <c r="DF50" s="125"/>
-      <c r="DG50" s="125"/>
-      <c r="DH50" s="125"/>
-      <c r="DI50" s="125"/>
-      <c r="DJ50" s="125"/>
-      <c r="DK50" s="125"/>
-      <c r="DL50" s="125"/>
-      <c r="DM50" s="125"/>
-      <c r="DN50" s="125"/>
-      <c r="DO50" s="126"/>
+      <c r="DB50" s="131"/>
+      <c r="DC50" s="131"/>
+      <c r="DD50" s="131"/>
+      <c r="DE50" s="131"/>
+      <c r="DF50" s="131"/>
+      <c r="DG50" s="131"/>
+      <c r="DH50" s="131"/>
+      <c r="DI50" s="131"/>
+      <c r="DJ50" s="131"/>
+      <c r="DK50" s="131"/>
+      <c r="DL50" s="131"/>
+      <c r="DM50" s="131"/>
+      <c r="DN50" s="131"/>
+      <c r="DO50" s="132"/>
       <c r="DP50" s="114"/>
       <c r="DQ50" s="32"/>
       <c r="DR50" s="32"/>
@@ -10421,20 +10421,20 @@
       <c r="CY51" s="32"/>
       <c r="CZ51" s="32"/>
       <c r="DA51" s="32"/>
-      <c r="DB51" s="125"/>
-      <c r="DC51" s="125"/>
-      <c r="DD51" s="125"/>
-      <c r="DE51" s="125"/>
-      <c r="DF51" s="125"/>
-      <c r="DG51" s="125"/>
-      <c r="DH51" s="125"/>
-      <c r="DI51" s="125"/>
-      <c r="DJ51" s="125"/>
-      <c r="DK51" s="125"/>
-      <c r="DL51" s="125"/>
-      <c r="DM51" s="125"/>
-      <c r="DN51" s="125"/>
-      <c r="DO51" s="126"/>
+      <c r="DB51" s="131"/>
+      <c r="DC51" s="131"/>
+      <c r="DD51" s="131"/>
+      <c r="DE51" s="131"/>
+      <c r="DF51" s="131"/>
+      <c r="DG51" s="131"/>
+      <c r="DH51" s="131"/>
+      <c r="DI51" s="131"/>
+      <c r="DJ51" s="131"/>
+      <c r="DK51" s="131"/>
+      <c r="DL51" s="131"/>
+      <c r="DM51" s="131"/>
+      <c r="DN51" s="131"/>
+      <c r="DO51" s="132"/>
       <c r="DP51" s="114"/>
       <c r="DQ51" s="32"/>
       <c r="DR51" s="32"/>
@@ -10577,20 +10577,20 @@
       <c r="CY52" s="32"/>
       <c r="CZ52" s="32"/>
       <c r="DA52" s="32"/>
-      <c r="DB52" s="125"/>
-      <c r="DC52" s="125"/>
-      <c r="DD52" s="125"/>
-      <c r="DE52" s="125"/>
-      <c r="DF52" s="125"/>
-      <c r="DG52" s="125"/>
-      <c r="DH52" s="125"/>
-      <c r="DI52" s="125"/>
-      <c r="DJ52" s="125"/>
-      <c r="DK52" s="125"/>
-      <c r="DL52" s="125"/>
-      <c r="DM52" s="125"/>
-      <c r="DN52" s="125"/>
-      <c r="DO52" s="126"/>
+      <c r="DB52" s="131"/>
+      <c r="DC52" s="131"/>
+      <c r="DD52" s="131"/>
+      <c r="DE52" s="131"/>
+      <c r="DF52" s="131"/>
+      <c r="DG52" s="131"/>
+      <c r="DH52" s="131"/>
+      <c r="DI52" s="131"/>
+      <c r="DJ52" s="131"/>
+      <c r="DK52" s="131"/>
+      <c r="DL52" s="131"/>
+      <c r="DM52" s="131"/>
+      <c r="DN52" s="131"/>
+      <c r="DO52" s="132"/>
       <c r="DP52" s="114"/>
       <c r="DQ52" s="32"/>
       <c r="DR52" s="32"/>
@@ -10733,20 +10733,20 @@
       <c r="CY53" s="32"/>
       <c r="CZ53" s="32"/>
       <c r="DA53" s="32"/>
-      <c r="DB53" s="125"/>
-      <c r="DC53" s="125"/>
-      <c r="DD53" s="125"/>
-      <c r="DE53" s="125"/>
-      <c r="DF53" s="125"/>
-      <c r="DG53" s="125"/>
-      <c r="DH53" s="125"/>
-      <c r="DI53" s="125"/>
-      <c r="DJ53" s="125"/>
-      <c r="DK53" s="125"/>
-      <c r="DL53" s="125"/>
-      <c r="DM53" s="125"/>
-      <c r="DN53" s="125"/>
-      <c r="DO53" s="126"/>
+      <c r="DB53" s="131"/>
+      <c r="DC53" s="131"/>
+      <c r="DD53" s="131"/>
+      <c r="DE53" s="131"/>
+      <c r="DF53" s="131"/>
+      <c r="DG53" s="131"/>
+      <c r="DH53" s="131"/>
+      <c r="DI53" s="131"/>
+      <c r="DJ53" s="131"/>
+      <c r="DK53" s="131"/>
+      <c r="DL53" s="131"/>
+      <c r="DM53" s="131"/>
+      <c r="DN53" s="131"/>
+      <c r="DO53" s="132"/>
       <c r="DP53" s="114"/>
       <c r="DQ53" s="32"/>
       <c r="DR53" s="32"/>
@@ -10881,20 +10881,20 @@
       <c r="CY54" s="32"/>
       <c r="CZ54" s="32"/>
       <c r="DA54" s="32"/>
-      <c r="DB54" s="125"/>
-      <c r="DC54" s="125"/>
-      <c r="DD54" s="125"/>
-      <c r="DE54" s="125"/>
-      <c r="DF54" s="125"/>
-      <c r="DG54" s="125"/>
-      <c r="DH54" s="125"/>
-      <c r="DI54" s="125"/>
-      <c r="DJ54" s="125"/>
-      <c r="DK54" s="125"/>
-      <c r="DL54" s="125"/>
-      <c r="DM54" s="125"/>
-      <c r="DN54" s="125"/>
-      <c r="DO54" s="126"/>
+      <c r="DB54" s="131"/>
+      <c r="DC54" s="131"/>
+      <c r="DD54" s="131"/>
+      <c r="DE54" s="131"/>
+      <c r="DF54" s="131"/>
+      <c r="DG54" s="131"/>
+      <c r="DH54" s="131"/>
+      <c r="DI54" s="131"/>
+      <c r="DJ54" s="131"/>
+      <c r="DK54" s="131"/>
+      <c r="DL54" s="131"/>
+      <c r="DM54" s="131"/>
+      <c r="DN54" s="131"/>
+      <c r="DO54" s="132"/>
       <c r="DP54" s="114"/>
       <c r="DQ54" s="32"/>
       <c r="DR54" s="32"/>
@@ -10922,12 +10922,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="DX4:EJ4"/>
-    <mergeCell ref="E5:E6"/>
     <mergeCell ref="P2:Y2"/>
     <mergeCell ref="P1:Y1"/>
     <mergeCell ref="H1:N1"/>
@@ -10937,6 +10931,12 @@
     <mergeCell ref="AJ4:BM4"/>
     <mergeCell ref="BN4:CR4"/>
     <mergeCell ref="CS4:DW4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="DX4:EJ4"/>
+    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C54">
     <cfRule type="dataBar" priority="61">
@@ -11028,14 +11028,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DB9">
-    <cfRule type="expression" dxfId="11" priority="152">
+    <cfRule type="expression" dxfId="11" priority="156" stopIfTrue="1">
+      <formula>AND(task_end&gt;=DF$5,task_start&lt;DG$5)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="152">
       <formula>AND(TODAY()&gt;=DF$5, TODAY()&lt;DG$5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="155">
+    <cfRule type="expression" dxfId="9" priority="155">
       <formula>AND(task_start&lt;=DF$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=DF$5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="9" priority="156" stopIfTrue="1">
-      <formula>AND(task_end&gt;=DF$5,task_start&lt;DG$5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EC9:EC16 EJ9:EJ16 EC41:EC44 EJ41:EJ44">
@@ -11130,15 +11130,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
@@ -11156,6 +11147,15 @@
     <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11471,14 +11471,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A82239A0-E68C-493F-BEE6-C77FEA397FD6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -11493,6 +11485,14 @@
     <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97245281-08F3-4104-84BD-39F3D8CFB195}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
